--- a/المرفقات/المرشدين/توزيع فترات الارشاد/توزيع فترات الارشاد محدث/تحديث/نماذج_جاهزة_للرفع/الاقتصاد والتمويل_طالبات.xlsx
+++ b/المرفقات/المرشدين/توزيع فترات الارشاد/توزيع فترات الارشاد محدث/تحديث/نماذج_جاهزة_للرفع/الاقتصاد والتمويل_طالبات.xlsx
@@ -32,9 +32,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
   <fonts count="1">
     <font>
       <sz val="12"/>
@@ -464,7 +461,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="str">
-        <v>أ. تماضر السلمي</v>
+        <v>ماجدة بنت شعبان بعناني</v>
       </c>
       <c r="C4" t="str">
         <v>307</v>
@@ -484,7 +481,7 @@
         <v>2</v>
       </c>
       <c r="B5" t="str">
-        <v>أ. تهاني الذبياني</v>
+        <v>اشواق علي طامي العتيبي</v>
       </c>
       <c r="C5" t="str">
         <v>107</v>
@@ -504,7 +501,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="str">
-        <v>أ. خديجة العتيبي</v>
+        <v>سمية محمد ابراهيم مجلد</v>
       </c>
       <c r="C6" t="str">
         <v>310</v>
@@ -524,7 +521,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="str">
-        <v>أ. رزان الطويرقي</v>
+        <v>رزان ابراهيم عاطي الطويرقي</v>
       </c>
       <c r="C7" t="str">
         <v>309</v>
@@ -544,7 +541,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="str">
-        <v>أ. زكية العوفي</v>
+        <v>سمية محمد ابراهيم مجلد</v>
       </c>
       <c r="C8" t="str">
         <v>310</v>
@@ -564,7 +561,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="str">
-        <v>د. أشواق السفياني</v>
+        <v>لجين خالد فيصل الحجري النمري</v>
       </c>
       <c r="C9" t="str">
         <v>119</v>
@@ -584,7 +581,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="str">
-        <v>د. أميرة عبدون</v>
+        <v>اميرة عثمان عبدون محمد</v>
       </c>
       <c r="C10" t="str">
         <v>108</v>
@@ -604,7 +601,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="str">
-        <v>د. إيمان العتيبي</v>
+        <v>حنان بنت محمد عامر</v>
       </c>
       <c r="C11" t="str">
         <v>311</v>
@@ -624,7 +621,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="str">
-        <v>د. انغام البريك</v>
+        <v>انغام بنت محرز البريك</v>
       </c>
       <c r="C12" t="str">
         <v>306</v>
@@ -644,7 +641,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="str">
-        <v>د. سمر عجيب</v>
+        <v>منال صالح عويمر السفياني</v>
       </c>
       <c r="C13" t="str">
         <v>308</v>
@@ -664,7 +661,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="str">
-        <v>د. ريم القحطاني</v>
+        <v>ريم عبدالمحسن محمد القحطاني</v>
       </c>
       <c r="C14" t="str">
         <v>305</v>
@@ -684,7 +681,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="str">
-        <v>د. سوليمة العبدلي</v>
+        <v>اميرة عثمان عبدون محمد</v>
       </c>
       <c r="C15" t="str">
         <v>108</v>
@@ -704,7 +701,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="str">
-        <v>د. غادة الكيلاني</v>
+        <v>حنان بنت محمد عامر</v>
       </c>
       <c r="C16" t="str">
         <v>311</v>
@@ -724,7 +721,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="str">
-        <v>د. غراس أبو الشامات</v>
+        <v>منال صالح عويمر السفياني</v>
       </c>
       <c r="C17" t="str">
         <v>308</v>
@@ -744,7 +741,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="str">
-        <v>د. فارعة الحربي</v>
+        <v>ريم عبدالمحسن محمد القحطاني</v>
       </c>
       <c r="C18" t="str">
         <v>305</v>
@@ -764,7 +761,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="str">
-        <v>د. ماجدة بعناني</v>
+        <v>ماجدة بنت شعبان بعناني</v>
       </c>
       <c r="C19" t="str">
         <v>307</v>
@@ -784,7 +781,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="str">
-        <v>د. منال السفياني</v>
+        <v>منال صالح عويمر السفياني</v>
       </c>
       <c r="C20" t="str">
         <v>308</v>
@@ -804,7 +801,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="str">
-        <v>د. نجلاء القاضي</v>
+        <v>اميرة عثمان عبدون محمد</v>
       </c>
       <c r="C21" t="str">
         <v>108</v>
@@ -824,7 +821,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="str">
-        <v>أ. أبرار الحربي</v>
+        <v>اشواق علي طامي العتيبي</v>
       </c>
       <c r="C22" t="str">
         <v>107</v>
@@ -844,7 +841,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="str">
-        <v>أ. أشواق العتيبي</v>
+        <v>اشواق علي طامي العتيبي</v>
       </c>
       <c r="C23" t="str">
         <v>107</v>
@@ -864,7 +861,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="str">
-        <v>أ. سمية مجلد</v>
+        <v>سمية محمد ابراهيم مجلد</v>
       </c>
       <c r="C24" t="str">
         <v>310</v>
@@ -884,7 +881,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="str">
-        <v>أ. لجين النمري</v>
+        <v>لجين خالد فيصل الحجري النمري</v>
       </c>
       <c r="C25" t="str">
         <v>119</v>
@@ -904,7 +901,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="str">
-        <v>أ. وفاء الأسمري</v>
+        <v>لجين خالد فيصل الحجري النمري</v>
       </c>
       <c r="C26" t="str">
         <v>119</v>
@@ -924,7 +921,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="str">
-        <v>د. حنان عامر</v>
+        <v>حنان بنت محمد عامر</v>
       </c>
       <c r="C27" t="str">
         <v>311</v>
@@ -944,7 +941,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="str">
-        <v>د. شيمة الزهراني</v>
+        <v>رزان ابراهيم عاطي الطويرقي</v>
       </c>
       <c r="C28" t="str">
         <v>309</v>
@@ -964,7 +961,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="str">
-        <v>د. مها قنصوة</v>
+        <v>انغام بنت محرز البريك</v>
       </c>
       <c r="C29" t="str">
         <v>306</v>

--- a/المرفقات/المرشدين/توزيع فترات الارشاد/توزيع فترات الارشاد محدث/تحديث/نماذج_جاهزة_للرفع/الاقتصاد والتمويل_طالبات.xlsx
+++ b/المرفقات/المرشدين/توزيع فترات الارشاد/توزيع فترات الارشاد محدث/تحديث/نماذج_جاهزة_للرفع/الاقتصاد والتمويل_طالبات.xlsx
@@ -461,7 +461,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="str">
-        <v>ماجدة بنت شعبان بعناني</v>
+        <v>تماضر عواض نفيع السلمي</v>
       </c>
       <c r="C4" t="str">
         <v>307</v>
@@ -481,7 +481,7 @@
         <v>2</v>
       </c>
       <c r="B5" t="str">
-        <v>اشواق علي طامي العتيبي</v>
+        <v>تهاني دخيل الله عطوان الزقله الذبياني</v>
       </c>
       <c r="C5" t="str">
         <v>107</v>
@@ -501,7 +501,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="str">
-        <v>سمية محمد ابراهيم مجلد</v>
+        <v>خديجة عواض زائد العتيبي</v>
       </c>
       <c r="C6" t="str">
         <v>310</v>
@@ -541,7 +541,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="str">
-        <v>سمية محمد ابراهيم مجلد</v>
+        <v>زكيه مرحوم شاهر الموسى العوفي</v>
       </c>
       <c r="C8" t="str">
         <v>310</v>
@@ -561,7 +561,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="str">
-        <v>لجين خالد فيصل الحجري النمري</v>
+        <v>أشواق عيظه عوض السفياني</v>
       </c>
       <c r="C9" t="str">
         <v>119</v>
@@ -601,7 +601,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="str">
-        <v>حنان بنت محمد عامر</v>
+        <v>ايمان سعد مشعان العتيبي</v>
       </c>
       <c r="C11" t="str">
         <v>311</v>
@@ -641,7 +641,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="str">
-        <v>منال صالح عويمر السفياني</v>
+        <v>سمر كامل محمد حسن عجيب</v>
       </c>
       <c r="C13" t="str">
         <v>308</v>
@@ -681,7 +681,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="str">
-        <v>اميرة عثمان عبدون محمد</v>
+        <v>سوليمة ابراهيم بلحسن العبدلي</v>
       </c>
       <c r="C15" t="str">
         <v>108</v>
@@ -701,7 +701,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="str">
-        <v>حنان بنت محمد عامر</v>
+        <v>غادة عبدالوهاب الكيلاني علي</v>
       </c>
       <c r="C16" t="str">
         <v>311</v>
@@ -721,7 +721,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="str">
-        <v>منال صالح عويمر السفياني</v>
+        <v>غراس غازي عبدالرحمن ابو الشامات</v>
       </c>
       <c r="C17" t="str">
         <v>308</v>
@@ -741,7 +741,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="str">
-        <v>ريم عبدالمحسن محمد القحطاني</v>
+        <v>فارعه محمد هليل السفري الحربي</v>
       </c>
       <c r="C18" t="str">
         <v>305</v>
@@ -801,7 +801,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="str">
-        <v>اميرة عثمان عبدون محمد</v>
+        <v>نجلاء فتح الرحمن احمد القاضي</v>
       </c>
       <c r="C21" t="str">
         <v>108</v>
@@ -821,7 +821,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="str">
-        <v>اشواق علي طامي العتيبي</v>
+        <v>ابرار سعد محمد الحربي</v>
       </c>
       <c r="C22" t="str">
         <v>107</v>
@@ -901,7 +901,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="str">
-        <v>لجين خالد فيصل الحجري النمري</v>
+        <v>وفاء محمد احمد الاسمري</v>
       </c>
       <c r="C26" t="str">
         <v>119</v>
@@ -941,7 +941,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="str">
-        <v>رزان ابراهيم عاطي الطويرقي</v>
+        <v>شيمه احمد مبارك الزهراني</v>
       </c>
       <c r="C28" t="str">
         <v>309</v>
@@ -961,7 +961,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="str">
-        <v>انغام بنت محرز البريك</v>
+        <v>مها مصطفي متولي قنصوه</v>
       </c>
       <c r="C29" t="str">
         <v>306</v>
